--- a/results/table/26_kor_task_top30_saved.xlsx
+++ b/results/table/26_kor_task_top30_saved.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="156">
   <si>
     <t>순위</t>
   </si>
@@ -75,15 +75,9 @@
     <t>Create graphs, charts, or other visualizations to convey the results of data analysis using specialized software.</t>
   </si>
   <si>
-    <t>Develop new visual design concepts and modify concepts based on stakeholder feedback.</t>
-  </si>
-  <si>
     <t>Revise written material to meet personal standards and to satisfy needs of clients, publishers, directors, or producers.</t>
   </si>
   <si>
-    <t>Archive documents, conduct research, and read copy, using the internet and various computer programs.</t>
-  </si>
-  <si>
     <t>Identify, develop, or evaluate marketing strategy, based on knowledge of establishment objectives, market characteristics, and cost and markup factors.</t>
   </si>
   <si>
@@ -114,6 +108,12 @@
     <t>Identify problems uncovered by testing or customer feedback, and correct problems or refer problems to appropriate personnel for correction.</t>
   </si>
   <si>
+    <t>Review files, records, and other documents to obtain information to respond to requests.</t>
+  </si>
+  <si>
+    <t>Write, update, and maintain computer programs or software packages to handle specific jobs such as tracking inventory, storing or retrieving data, or controlling other equipment.</t>
+  </si>
+  <si>
     <t>O*NET-SOC 코드</t>
   </si>
   <si>
@@ -168,43 +168,43 @@
     <t>15-2051.00</t>
   </si>
   <si>
+    <t>27-3043.05</t>
+  </si>
+  <si>
+    <t>11-2021.00</t>
+  </si>
+  <si>
+    <t>25-9031.00</t>
+  </si>
+  <si>
+    <t>51-8021.00</t>
+  </si>
+  <si>
+    <t>11-2011.00</t>
+  </si>
+  <si>
+    <t>11-3051.01</t>
+  </si>
+  <si>
+    <t>17-3025.00</t>
+  </si>
+  <si>
+    <t>43-4111.00</t>
+  </si>
+  <si>
+    <t>43-1011.00</t>
+  </si>
+  <si>
+    <t>27-3091.00</t>
+  </si>
+  <si>
     <t>15-1255.00</t>
   </si>
   <si>
-    <t>27-3043.05</t>
-  </si>
-  <si>
-    <t>43-9081.00</t>
-  </si>
-  <si>
-    <t>11-2021.00</t>
-  </si>
-  <si>
-    <t>25-9031.00</t>
-  </si>
-  <si>
-    <t>51-8021.00</t>
-  </si>
-  <si>
-    <t>11-2011.00</t>
-  </si>
-  <si>
-    <t>11-3051.01</t>
-  </si>
-  <si>
-    <t>17-3025.00</t>
-  </si>
-  <si>
-    <t>43-4111.00</t>
-  </si>
-  <si>
-    <t>43-1011.00</t>
-  </si>
-  <si>
-    <t>27-3091.00</t>
-  </si>
-  <si>
-    <t>15-1255.00</t>
+    <t>43-9061.00</t>
+  </si>
+  <si>
+    <t>15-1251.00</t>
   </si>
   <si>
     <t>직업(O*NET-SOC)</t>
@@ -261,43 +261,43 @@
     <t>Data Scientists</t>
   </si>
   <si>
+    <t>Poets, Lyricists and Creative Writers</t>
+  </si>
+  <si>
+    <t>Marketing Managers</t>
+  </si>
+  <si>
+    <t>Instructional Coordinators</t>
+  </si>
+  <si>
+    <t>Stationary Engineers and Boiler Operators</t>
+  </si>
+  <si>
+    <t>Advertising and Promotions Managers</t>
+  </si>
+  <si>
+    <t>Quality Control Systems Managers</t>
+  </si>
+  <si>
+    <t>Environmental Engineering Technologists and Technicians</t>
+  </si>
+  <si>
+    <t>Interviewers, Except Eligibility and Loan</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Office and Administrative Support Workers</t>
+  </si>
+  <si>
+    <t>Interpreters and Translators</t>
+  </si>
+  <si>
     <t>Web and Digital Interface Designers</t>
   </si>
   <si>
-    <t>Poets, Lyricists and Creative Writers</t>
-  </si>
-  <si>
-    <t>Proofreaders and Copy Markers</t>
-  </si>
-  <si>
-    <t>Marketing Managers</t>
-  </si>
-  <si>
-    <t>Instructional Coordinators</t>
-  </si>
-  <si>
-    <t>Stationary Engineers and Boiler Operators</t>
-  </si>
-  <si>
-    <t>Advertising and Promotions Managers</t>
-  </si>
-  <si>
-    <t>Quality Control Systems Managers</t>
-  </si>
-  <si>
-    <t>Environmental Engineering Technologists and Technicians</t>
-  </si>
-  <si>
-    <t>Interviewers, Except Eligibility and Loan</t>
-  </si>
-  <si>
-    <t>First-Line Supervisors of Office and Administrative Support Workers</t>
-  </si>
-  <si>
-    <t>Interpreters and Translators</t>
-  </si>
-  <si>
-    <t>Web and Digital Interface Designers</t>
+    <t>Office Clerks, General</t>
+  </si>
+  <si>
+    <t>Computer Programmers</t>
   </si>
   <si>
     <t>SOC 2018 6자리</t>
@@ -351,43 +351,43 @@
     <t>15-2051</t>
   </si>
   <si>
+    <t>27-3043</t>
+  </si>
+  <si>
+    <t>11-2021</t>
+  </si>
+  <si>
+    <t>25-9031</t>
+  </si>
+  <si>
+    <t>51-8021</t>
+  </si>
+  <si>
+    <t>11-2011</t>
+  </si>
+  <si>
+    <t>11-3051</t>
+  </si>
+  <si>
+    <t>17-3025</t>
+  </si>
+  <si>
+    <t>43-4111</t>
+  </si>
+  <si>
+    <t>43-1011</t>
+  </si>
+  <si>
+    <t>27-3091</t>
+  </si>
+  <si>
     <t>15-1255</t>
   </si>
   <si>
-    <t>27-3043</t>
-  </si>
-  <si>
-    <t>43-9081</t>
-  </si>
-  <si>
-    <t>11-2021</t>
-  </si>
-  <si>
-    <t>25-9031</t>
-  </si>
-  <si>
-    <t>51-8021</t>
-  </si>
-  <si>
-    <t>11-2011</t>
-  </si>
-  <si>
-    <t>11-3051</t>
-  </si>
-  <si>
-    <t>17-3025</t>
-  </si>
-  <si>
-    <t>43-4111</t>
-  </si>
-  <si>
-    <t>43-1011</t>
-  </si>
-  <si>
-    <t>27-3091</t>
-  </si>
-  <si>
-    <t>15-1255</t>
+    <t>43-9061</t>
+  </si>
+  <si>
+    <t>15-1251</t>
   </si>
   <si>
     <t>SOC 대분류</t>
@@ -432,34 +432,37 @@
     <t>Arts, Design, Entertainment, Sports, and Media</t>
   </si>
   <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Educational Instruction and Library</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Architecture and Engineering</t>
+  </si>
+  <si>
     <t>Office and Administrative Support</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
-    <t>Educational Instruction and Library</t>
-  </si>
-  <si>
-    <t>Production</t>
-  </si>
-  <si>
-    <t>Management</t>
-  </si>
-  <si>
-    <t>Architecture and Engineering</t>
+    <t>Arts, Design, Entertainment, Sports, and Media</t>
+  </si>
+  <si>
+    <t>Computer and Mathematical</t>
   </si>
   <si>
     <t>Office and Administrative Support</t>
   </si>
   <si>
-    <t>Arts, Design, Entertainment, Sports, and Media</t>
-  </si>
-  <si>
     <t>Computer and Mathematical</t>
   </si>
   <si>
-    <t>월평균 절감 시간(시간, K = 3) = 대화 수 × 대화당 절감 시간</t>
+    <t>비중 × 대화당 절감 시간(분, 두 달 평균)</t>
   </si>
   <si>
     <t>한국 task 절감 시간 중 비중(%)</t>
@@ -468,7 +471,7 @@
     <t>누적 비중(%)</t>
   </si>
   <si>
-    <t>월평균 업무용 대화 수(K = 3)</t>
+    <t>한국 업무용 대화 중 비중(%, 두 달 단순평균)</t>
   </si>
   <si>
     <t>대화당 절감 시간(분, GLOBAL)</t>
@@ -549,25 +552,25 @@
         <v>125</v>
       </c>
       <c r="H1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2">
@@ -593,16 +596,16 @@
         <v>126</v>
       </c>
       <c r="H2" s="1">
-        <v>47232673.256150715</v>
+        <v>8.1876758183771514</v>
       </c>
       <c r="I2" s="1">
-        <v>2.948503187059254</v>
+        <v>3.1003147091480558</v>
       </c>
       <c r="J2" s="1">
-        <v>2.948503187059254</v>
+        <v>3.1003147091480558</v>
       </c>
       <c r="K2" s="1">
-        <v>6137561.2074999493</v>
+        <v>1.7732203161545261</v>
       </c>
       <c r="L2" s="1">
         <v>461.74046979865761</v>
@@ -637,16 +640,16 @@
         <v>126</v>
       </c>
       <c r="H3" s="1">
-        <v>43639880.766188174</v>
+        <v>7.5646705938443315</v>
       </c>
       <c r="I3" s="1">
-        <v>2.7242228451517034</v>
+        <v>2.8644098804346458</v>
       </c>
       <c r="J3" s="1">
-        <v>5.6727260322109574</v>
+        <v>5.9647245895827012</v>
       </c>
       <c r="K3" s="1">
-        <v>24785912.977437481</v>
+        <v>7.1607767845261572</v>
       </c>
       <c r="L3" s="1">
         <v>105.64036307053942</v>
@@ -681,16 +684,16 @@
         <v>127</v>
       </c>
       <c r="H4" s="1">
-        <v>21995949.204833984</v>
+        <v>3.8127465500879332</v>
       </c>
       <c r="I4" s="1">
-        <v>1.3730987865354609</v>
+        <v>1.4437203516240416</v>
       </c>
       <c r="J4" s="1">
-        <v>7.0458248187464179</v>
+        <v>7.408444941206743</v>
       </c>
       <c r="K4" s="1">
-        <v>5065623.0890156049</v>
+        <v>1.4634465022651735</v>
       </c>
       <c r="L4" s="1">
         <v>260.53200743494426</v>
@@ -725,16 +728,16 @@
         <v>128</v>
       </c>
       <c r="H5" s="1">
-        <v>21702737.430246264</v>
+        <v>3.7618818803565466</v>
       </c>
       <c r="I5" s="1">
-        <v>1.3547950194129295</v>
+        <v>1.4244601259822021</v>
       </c>
       <c r="J5" s="1">
-        <v>8.4006198381593471</v>
+        <v>8.8329050671889444</v>
       </c>
       <c r="K5" s="1">
-        <v>4867141.0315156672</v>
+        <v>1.4060906459724036</v>
       </c>
       <c r="L5" s="1">
         <v>267.54191780821918</v>
@@ -769,16 +772,16 @@
         <v>129</v>
       </c>
       <c r="H6" s="1">
-        <v>21252735.594865263</v>
+        <v>3.6840073928484323</v>
       </c>
       <c r="I6" s="1">
-        <v>1.3267036209310406</v>
+        <v>1.3949724637390446</v>
       </c>
       <c r="J6" s="1">
-        <v>9.7273234590903872</v>
+        <v>10.227877530927989</v>
       </c>
       <c r="K6" s="1">
-        <v>4182731.6922703544</v>
+        <v>1.2084102779650587</v>
       </c>
       <c r="L6" s="1">
         <v>304.86395721925129</v>
@@ -813,16 +816,16 @@
         <v>129</v>
       </c>
       <c r="H7" s="1">
-        <v>20737587.672373861</v>
+        <v>3.5948238985353327</v>
       </c>
       <c r="I7" s="1">
-        <v>1.2945454730524415</v>
+        <v>1.361202575266967</v>
       </c>
       <c r="J7" s="1">
-        <v>11.021868932142828</v>
+        <v>11.589080106194956</v>
       </c>
       <c r="K7" s="1">
-        <v>1829468.5204037135</v>
+        <v>0.52855851756297911</v>
       </c>
       <c r="L7" s="1">
         <v>680.11843137254903</v>
@@ -857,16 +860,16 @@
         <v>129</v>
       </c>
       <c r="H8" s="1">
-        <v>20423502.62964724</v>
+        <v>3.5403743837707005</v>
       </c>
       <c r="I8" s="1">
-        <v>1.2749386905935109</v>
+        <v>1.3405849256096771</v>
       </c>
       <c r="J8" s="1">
-        <v>12.296807622736338</v>
+        <v>12.929665031804634</v>
       </c>
       <c r="K8" s="1">
-        <v>3995774.866820801</v>
+        <v>1.1544329783791754</v>
       </c>
       <c r="L8" s="1">
         <v>306.67647668393784</v>
@@ -901,16 +904,16 @@
         <v>130</v>
       </c>
       <c r="H9" s="1">
-        <v>19418777.483016081</v>
+        <v>3.3660971058635774</v>
       </c>
       <c r="I9" s="1">
-        <v>1.2122186476076997</v>
+        <v>1.2745937432337204</v>
       </c>
       <c r="J9" s="1">
-        <v>13.509026270344037</v>
+        <v>14.204258775038355</v>
       </c>
       <c r="K9" s="1">
-        <v>6141277.0863395296</v>
+        <v>1.7742393107834167</v>
       </c>
       <c r="L9" s="1">
         <v>189.72057971014488</v>
@@ -945,16 +948,16 @@
         <v>131</v>
       </c>
       <c r="H10" s="1">
-        <v>19182860.231255691</v>
+        <v>3.3254439181743427</v>
       </c>
       <c r="I10" s="1">
-        <v>1.1974914953898823</v>
+        <v>1.2592001591980897</v>
       </c>
       <c r="J10" s="1">
-        <v>14.706517765733921</v>
+        <v>15.463458934236444</v>
       </c>
       <c r="K10" s="1">
-        <v>2543776.767021744</v>
+        <v>0.73496052179805038</v>
       </c>
       <c r="L10" s="1">
         <v>452.46565217391304</v>
@@ -989,16 +992,16 @@
         <v>132</v>
       </c>
       <c r="H11" s="1">
-        <v>19027182.388573062</v>
+        <v>3.2982209752642246</v>
       </c>
       <c r="I11" s="1">
-        <v>1.1877732943298891</v>
+        <v>1.2488920214307024</v>
       </c>
       <c r="J11" s="1">
-        <v>15.894291060063809</v>
+        <v>16.712350955667148</v>
       </c>
       <c r="K11" s="1">
-        <v>2638883.1819430068</v>
+        <v>0.76238471924105944</v>
       </c>
       <c r="L11" s="1">
         <v>432.61897727272725</v>
@@ -1033,16 +1036,16 @@
         <v>132</v>
       </c>
       <c r="H12" s="1">
-        <v>18500938.84267512</v>
+        <v>3.2070453398030039</v>
       </c>
       <c r="I12" s="1">
-        <v>1.1549225013240667</v>
+        <v>1.2143677962407056</v>
       </c>
       <c r="J12" s="1">
-        <v>17.049213561387877</v>
+        <v>17.926718751907853</v>
       </c>
       <c r="K12" s="1">
-        <v>5399002.1919227308</v>
+        <v>1.5598167716812272</v>
       </c>
       <c r="L12" s="1">
         <v>205.60397849462368</v>
@@ -1077,16 +1080,16 @@
         <v>132</v>
       </c>
       <c r="H13" s="1">
-        <v>18340377.272943549</v>
+        <v>3.179218973198243</v>
       </c>
       <c r="I13" s="1">
-        <v>1.1448994332350479</v>
+        <v>1.2038311683134917</v>
       </c>
       <c r="J13" s="1">
-        <v>18.194112994622923</v>
+        <v>19.130549920221345</v>
       </c>
       <c r="K13" s="1">
-        <v>3887410.5631533712</v>
+        <v>1.1231075234587138</v>
       </c>
       <c r="L13" s="1">
         <v>283.07342857142862</v>
@@ -1121,16 +1124,16 @@
         <v>133</v>
       </c>
       <c r="H14" s="1">
-        <v>17020112.696515709</v>
+        <v>2.9502589029949617</v>
       </c>
       <c r="I14" s="1">
-        <v>1.0624818175678679</v>
+        <v>1.117134004282454</v>
       </c>
       <c r="J14" s="1">
-        <v>19.256594812190791</v>
+        <v>20.2476839245038</v>
       </c>
       <c r="K14" s="1">
-        <v>9535718.8834685683</v>
+        <v>2.7548622458269194</v>
       </c>
       <c r="L14" s="1">
         <v>107.09279229711142</v>
@@ -1165,16 +1168,16 @@
         <v>134</v>
       </c>
       <c r="H15" s="1">
-        <v>16956174.426102825</v>
+        <v>2.9393666357351513</v>
       </c>
       <c r="I15" s="1">
-        <v>1.0584904662195109</v>
+        <v>1.1130095790913923</v>
       </c>
       <c r="J15" s="1">
-        <v>20.315085278410301</v>
+        <v>21.360693503595193</v>
       </c>
       <c r="K15" s="1">
-        <v>1589790.3952966984</v>
+        <v>0.45931909799905474</v>
       </c>
       <c r="L15" s="1">
         <v>639.94000000000005</v>
@@ -1209,16 +1212,16 @@
         <v>135</v>
       </c>
       <c r="H16" s="1">
-        <v>16447380.610517617</v>
+        <v>2.8512119097614765</v>
       </c>
       <c r="I16" s="1">
-        <v>1.0267289739433212</v>
+        <v>1.0796292401918399</v>
       </c>
       <c r="J16" s="1">
-        <v>21.341814252353622</v>
+        <v>22.440322743787032</v>
       </c>
       <c r="K16" s="1">
-        <v>1993310.3166911295</v>
+        <v>0.57591238481320162</v>
       </c>
       <c r="L16" s="1">
         <v>495.07737373737376</v>
@@ -1253,16 +1256,16 @@
         <v>136</v>
       </c>
       <c r="H17" s="1">
-        <v>16355634.688242441</v>
+        <v>2.835125956460423</v>
       </c>
       <c r="I17" s="1">
-        <v>1.0210017278321173</v>
+        <v>1.0735381932651908</v>
       </c>
       <c r="J17" s="1">
-        <v>22.36281598018574</v>
+        <v>23.513860937052222</v>
       </c>
       <c r="K17" s="1">
-        <v>2064739.4080512314</v>
+        <v>0.59651168141469191</v>
       </c>
       <c r="L17" s="1">
         <v>475.28423076923076</v>
@@ -1297,16 +1300,16 @@
         <v>137</v>
       </c>
       <c r="H18" s="1">
-        <v>16253175.916070266</v>
+        <v>2.8174137391225997</v>
       </c>
       <c r="I18" s="1">
-        <v>1.0146057312588661</v>
+        <v>1.06683135127948</v>
       </c>
       <c r="J18" s="1">
-        <v>23.377421711444605</v>
+        <v>24.580692288331701</v>
       </c>
       <c r="K18" s="1">
-        <v>2285225.0869251988</v>
+        <v>0.66022220212407046</v>
       </c>
       <c r="L18" s="1">
         <v>426.73720000000003</v>
@@ -1323,7 +1326,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>21694</v>
+        <v>11046</v>
       </c>
       <c r="C19" t="s">
         <v>20</v>
@@ -1338,28 +1341,28 @@
         <v>112</v>
       </c>
       <c r="G19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H19" s="1">
-        <v>16201962.88658135</v>
+        <v>2.6951429410229775</v>
       </c>
       <c r="I19" s="1">
-        <v>1.0114087540340515</v>
+        <v>1.0205327480792048</v>
       </c>
       <c r="J19" s="1">
-        <v>24.388830465478655</v>
+        <v>25.601225036410906</v>
       </c>
       <c r="K19" s="1">
-        <v>2265569.6344841435</v>
+        <v>1.3310903981732902</v>
       </c>
       <c r="L19" s="1">
-        <v>429.08315789473687</v>
+        <v>202.47632653061225</v>
       </c>
       <c r="M19" s="1">
-        <v>0.47999999999999998</v>
+        <v>0.95999999999999996</v>
       </c>
       <c r="N19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1367,7 +1370,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>11046</v>
+        <v>951</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
@@ -1382,25 +1385,25 @@
         <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H20" s="1">
-        <v>15547824.40579937</v>
+        <v>2.5788937890705244</v>
       </c>
       <c r="I20" s="1">
-        <v>0.97057411008104155</v>
+        <v>0.97651427889222964</v>
       </c>
       <c r="J20" s="1">
-        <v>25.359404575559697</v>
+        <v>26.577739315303134</v>
       </c>
       <c r="K20" s="1">
-        <v>4607301.4081817716</v>
+        <v>0.48071880431252356</v>
       </c>
       <c r="L20" s="1">
-        <v>202.47632653061225</v>
+        <v>536.46617647058827</v>
       </c>
       <c r="M20" s="1">
-        <v>0.95999999999999996</v>
+        <v>0.255</v>
       </c>
       <c r="N20" s="1">
         <v>2</v>
@@ -1411,7 +1414,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>20908</v>
+        <v>22444</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
@@ -1426,28 +1429,28 @@
         <v>114</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H21" s="1">
-        <v>15168823.253578881</v>
+        <v>2.5764725905969676</v>
       </c>
       <c r="I21" s="1">
-        <v>0.94691493459544229</v>
+        <v>0.97559747693183851</v>
       </c>
       <c r="J21" s="1">
-        <v>26.306319510155138</v>
+        <v>27.553336792234973</v>
       </c>
       <c r="K21" s="1">
-        <v>2402000.6342112534</v>
+        <v>0.49154816525467493</v>
       </c>
       <c r="L21" s="1">
-        <v>378.90472727272726</v>
+        <v>524.15465517241364</v>
       </c>
       <c r="M21" s="1">
-        <v>0.41999999999999998</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="N21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1455,7 +1458,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>951</v>
+        <v>10475</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
@@ -1470,25 +1473,25 @@
         <v>115</v>
       </c>
       <c r="G22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H22" s="1">
-        <v>14877067.420113157</v>
+        <v>2.4706913015557324</v>
       </c>
       <c r="I22" s="1">
-        <v>0.92870205470715872</v>
+        <v>0.93554272957226525</v>
       </c>
       <c r="J22" s="1">
-        <v>27.235021564862297</v>
+        <v>28.488879521807238</v>
       </c>
       <c r="K22" s="1">
-        <v>1663896.2237644959</v>
+        <v>0.79961810219164109</v>
       </c>
       <c r="L22" s="1">
-        <v>536.46617647058827</v>
+        <v>308.98391304347837</v>
       </c>
       <c r="M22" s="1">
-        <v>0.255</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="N22" s="1">
         <v>2</v>
@@ -1499,7 +1502,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>22444</v>
+        <v>21222</v>
       </c>
       <c r="C23" t="s">
         <v>24</v>
@@ -1514,25 +1517,25 @@
         <v>116</v>
       </c>
       <c r="G23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H23" s="1">
-        <v>14862751.346695039</v>
+        <v>2.4075178435823887</v>
       </c>
       <c r="I23" s="1">
-        <v>0.9278083727452977</v>
+        <v>0.91162170420107225</v>
       </c>
       <c r="J23" s="1">
-        <v>28.162829937607594</v>
+        <v>29.400501226008309</v>
       </c>
       <c r="K23" s="1">
-        <v>1701339.6179957006</v>
+        <v>0.67986892494878481</v>
       </c>
       <c r="L23" s="1">
-        <v>524.15465517241364</v>
+        <v>354.1149999999999</v>
       </c>
       <c r="M23" s="1">
-        <v>0.67500000000000004</v>
+        <v>0.35999999999999999</v>
       </c>
       <c r="N23" s="1">
         <v>2</v>
@@ -1543,7 +1546,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>10475</v>
+        <v>15417</v>
       </c>
       <c r="C24" t="s">
         <v>25</v>
@@ -1561,22 +1564,22 @@
         <v>142</v>
       </c>
       <c r="H24" s="1">
-        <v>14252763.827864703</v>
+        <v>2.3918992213104397</v>
       </c>
       <c r="I24" s="1">
-        <v>0.88972985591895226</v>
+        <v>0.90570761509440945</v>
       </c>
       <c r="J24" s="1">
-        <v>29.052559793526544</v>
+        <v>30.30620884110272</v>
       </c>
       <c r="K24" s="1">
-        <v>2767671.0455522919</v>
+        <v>0.33020683267470408</v>
       </c>
       <c r="L24" s="1">
-        <v>308.98391304347837</v>
+        <v>724.36393939393929</v>
       </c>
       <c r="M24" s="1">
-        <v>0.38500000000000001</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="N24" s="1">
         <v>2</v>
@@ -1587,7 +1590,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>21222</v>
+        <v>3644</v>
       </c>
       <c r="C25" t="s">
         <v>26</v>
@@ -1605,22 +1608,22 @@
         <v>143</v>
       </c>
       <c r="H25" s="1">
-        <v>13888795.139705569</v>
+        <v>2.3696136829122025</v>
       </c>
       <c r="I25" s="1">
-        <v>0.86700908313509895</v>
+        <v>0.89726905645701671</v>
       </c>
       <c r="J25" s="1">
-        <v>29.919568876661643</v>
+        <v>31.203477897559736</v>
       </c>
       <c r="K25" s="1">
-        <v>2353268.5946156881</v>
+        <v>0.6249096589104236</v>
       </c>
       <c r="L25" s="1">
-        <v>354.1149999999999</v>
+        <v>379.19299999999998</v>
       </c>
       <c r="M25" s="1">
-        <v>0.35999999999999999</v>
+        <v>0.26000000000000001</v>
       </c>
       <c r="N25" s="1">
         <v>2</v>
@@ -1631,7 +1634,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>15417</v>
+        <v>2637</v>
       </c>
       <c r="C26" t="s">
         <v>27</v>
@@ -1646,25 +1649,25 @@
         <v>119</v>
       </c>
       <c r="G26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H26" s="1">
-        <v>13798520.031248022</v>
+        <v>2.2942132771116404</v>
       </c>
       <c r="I26" s="1">
-        <v>0.8613736526872886</v>
+        <v>0.8687182207418882</v>
       </c>
       <c r="J26" s="1">
-        <v>30.78094252934893</v>
+        <v>32.072196118301626</v>
       </c>
       <c r="K26" s="1">
-        <v>1142949.2232420873</v>
+        <v>0.42759233066286356</v>
       </c>
       <c r="L26" s="1">
-        <v>724.36393939393929</v>
+        <v>536.54219512195118</v>
       </c>
       <c r="M26" s="1">
-        <v>0.17499999999999999</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="N26" s="1">
         <v>2</v>
@@ -1675,7 +1678,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>3644</v>
+        <v>9716</v>
       </c>
       <c r="C27" t="s">
         <v>28</v>
@@ -1693,22 +1696,22 @@
         <v>144</v>
       </c>
       <c r="H27" s="1">
-        <v>13670018.767356668</v>
+        <v>2.2502905828817803</v>
       </c>
       <c r="I27" s="1">
-        <v>0.85335195160613153</v>
+        <v>0.85208661758527493</v>
       </c>
       <c r="J27" s="1">
-        <v>31.634294480955063</v>
+        <v>32.924282735886898</v>
       </c>
       <c r="K27" s="1">
-        <v>2163017.5821847981</v>
+        <v>0.39569375199039558</v>
       </c>
       <c r="L27" s="1">
-        <v>379.19299999999998</v>
+        <v>568.69500000000005</v>
       </c>
       <c r="M27" s="1">
-        <v>0.26000000000000001</v>
+        <v>0.245</v>
       </c>
       <c r="N27" s="1">
         <v>2</v>
@@ -1719,7 +1722,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>2637</v>
+        <v>9331</v>
       </c>
       <c r="C28" t="s">
         <v>29</v>
@@ -1737,22 +1740,22 @@
         <v>145</v>
       </c>
       <c r="H28" s="1">
-        <v>13234945.018120127</v>
+        <v>2.0939307299806069</v>
       </c>
       <c r="I28" s="1">
-        <v>0.82619244002666137</v>
+        <v>0.7928799803633072</v>
       </c>
       <c r="J28" s="1">
-        <v>32.460486920981722</v>
+        <v>33.717162716250208</v>
       </c>
       <c r="K28" s="1">
-        <v>1480026.5632542032</v>
+        <v>1.3246507337856774</v>
       </c>
       <c r="L28" s="1">
-        <v>536.54219512195118</v>
+        <v>158.07417582417582</v>
       </c>
       <c r="M28" s="1">
-        <v>0.26500000000000001</v>
+        <v>0.95500000000000007</v>
       </c>
       <c r="N28" s="1">
         <v>2</v>
@@ -1763,7 +1766,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>9716</v>
+        <v>21702</v>
       </c>
       <c r="C29" t="s">
         <v>30</v>
@@ -1778,25 +1781,25 @@
         <v>122</v>
       </c>
       <c r="G29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H29" s="1">
-        <v>12981339.251662605</v>
+        <v>2.0751387113064403</v>
       </c>
       <c r="I29" s="1">
-        <v>0.81036108094602255</v>
+        <v>0.78576426484128592</v>
       </c>
       <c r="J29" s="1">
-        <v>33.270848001927746</v>
+        <v>34.502926981091491</v>
       </c>
       <c r="K29" s="1">
-        <v>1369592.4091116611</v>
+        <v>0.41079711060949015</v>
       </c>
       <c r="L29" s="1">
-        <v>568.69500000000005</v>
+        <v>505.14929577464784</v>
       </c>
       <c r="M29" s="1">
-        <v>0.245</v>
+        <v>0.29500000000000004</v>
       </c>
       <c r="N29" s="1">
         <v>2</v>
@@ -1807,7 +1810,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>9331</v>
+        <v>834</v>
       </c>
       <c r="C30" t="s">
         <v>31</v>
@@ -1822,25 +1825,25 @@
         <v>123</v>
       </c>
       <c r="G30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H30" s="1">
-        <v>12079283.878553668</v>
+        <v>2.0573725598847932</v>
       </c>
       <c r="I30" s="1">
-        <v>0.75405020630863839</v>
+        <v>0.77903700037707069</v>
       </c>
       <c r="J30" s="1">
-        <v>34.024898208236387</v>
+        <v>35.281963981468564</v>
       </c>
       <c r="K30" s="1">
-        <v>4584917.358793376</v>
+        <v>1.1311619557796095</v>
       </c>
       <c r="L30" s="1">
-        <v>158.07417582417582</v>
+        <v>181.88134328358211</v>
       </c>
       <c r="M30" s="1">
-        <v>0.95500000000000007</v>
+        <v>0.69999999999999996</v>
       </c>
       <c r="N30" s="1">
         <v>2</v>
@@ -1851,7 +1854,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>21702</v>
+        <v>1270</v>
       </c>
       <c r="C31" t="s">
         <v>32</v>
@@ -1866,25 +1869,25 @@
         <v>124</v>
       </c>
       <c r="G31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H31" s="1">
-        <v>11970620.888825424</v>
+        <v>2.0418475581841058</v>
       </c>
       <c r="I31" s="1">
-        <v>0.74726691098695364</v>
+        <v>0.77315836128584559</v>
       </c>
       <c r="J31" s="1">
-        <v>34.772165119223338</v>
+        <v>36.055122342754409</v>
       </c>
       <c r="K31" s="1">
-        <v>1421831.6433127094</v>
+        <v>0.35410012628272991</v>
       </c>
       <c r="L31" s="1">
-        <v>505.14929577464784</v>
+        <v>576.63000000000011</v>
       </c>
       <c r="M31" s="1">
-        <v>0.29500000000000004</v>
+        <v>0.255</v>
       </c>
       <c r="N31" s="1">
         <v>2</v>
